--- a/data/master_bills.xlsx
+++ b/data/master_bills.xlsx
@@ -3988,13 +3988,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>미납</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+          <t>수납</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>간편결제</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>네이버페이체크</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:02:34</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>73864516</v>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>

--- a/data/master_bills.xlsx
+++ b/data/master_bills.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>미납</t>
+          <t>파기</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -675,8 +675,16 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:32:08</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>전화번호 입력 오류</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -716,7 +724,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>미납</t>
+          <t>파기</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -726,8 +734,16 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:31:58</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>전화번호 입력 오류</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/data/master_bills.xlsx
+++ b/data/master_bills.xlsx
@@ -545,7 +545,7 @@
         <v>540000</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>540000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -563,14 +563,32 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>미납</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>수납</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>청구서 결제 ・ 삼성카드사</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>앱카드</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>삼성개인특별카드</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:21:13</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>36395221</v>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -596,7 +614,7 @@
         <v>480000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>480000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -614,14 +632,32 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>미납</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>수납</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>청구서 결제 ・ 삼성카드사</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>앱카드</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>삼성개인특별카드</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:19:47</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>59016778</v>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
